--- a/output/normalised.xlsx
+++ b/output/normalised.xlsx
@@ -5979,7 +5979,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Graham Barber</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">21/07/2026 01/12/2026</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Graham Barber</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Jennie Agustin</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Anu Joshi</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Graham Barber; Graham Barber; Anu Joshi</t>
+          <t xml:space="preserve">Graham Barber</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICTCLD301 Evaluate Characteristics of Cloud Computing solutions and services | ICTICT310 Identify and use industry specific technologies.</t>
+          <t xml:space="preserve">ICTCLD301 Evaluate Characteristics of Cloud Computing solutions and services</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICTCLD301, ICTICT310</t>
+          <t xml:space="preserve">ICTCLD301</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7165,17 +7165,17 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-14 14-18</t>
+          <t xml:space="preserve">10-14</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t xml:space="preserve">24/09/2026 29/10/2026 5/11/2026 03/12/202</t>
+          <t xml:space="preserve">24/09/2026 29/10/2026</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Graham Barber</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7197,17 +7197,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICT40120 Cert IV  Programming OUR.docx</t>
+          <t xml:space="preserve">ICT30120 Cert III General VOF OUR.docx</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cert IV Programming</t>
+          <t xml:space="preserve">Cert III General (VOFF)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICT40120</t>
+          <t xml:space="preserve">ICT30120</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monday</t>
+          <t xml:space="preserve">Thursday</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1a Mon 1b Mon</t>
+          <t xml:space="preserve">3A Thu 3B Thu 3C Thu</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:00</t>
+          <t xml:space="preserve">2:30</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7242,37 +7242,37 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">BSBXCS404 Contribute to cyber security risk management. | ICTICT443 Work collaboratively in the ICT industry | ICTICT451 Comply with IP, ethics and privacy policies in ICT environments</t>
+          <t xml:space="preserve">ICTICT310 Identify and use industry specific technologies.</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">BSBXCS404, ICTICT443, ICTICT451</t>
+          <t xml:space="preserve">ICTICT310</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Graham on Campus</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-8</t>
+          <t xml:space="preserve">14-18</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t xml:space="preserve">20/07/2026 7/09/2026</t>
+          <t xml:space="preserve">5/11/2026 03/12/202</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Graham Barber and; Rima Andrews</t>
+          <t xml:space="preserve">Anu Joshi</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2F</t>
+          <t xml:space="preserve">VOFF</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
     </row>
@@ -7334,12 +7334,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">BSBCRT404 Apply advanced critical thinking to work processes | ICTICT426 Identify and evaluate emerging technologies and practices | ICTSAS432 Identify and resolve client ICT problems</t>
+          <t xml:space="preserve">BSBXCS404 Contribute to cyber security risk management. | ICTICT443 Work collaboratively in the ICT industry | ICTICT451 Comply with IP, ethics and privacy policies in ICT environments</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">BSBCRT404, ICTICT426, ICTSAS432</t>
+          <t xml:space="preserve">BSBXCS404, ICTICT443, ICTICT451</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7349,17 +7349,17 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9-18</t>
+          <t xml:space="preserve">1-8</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t xml:space="preserve">14/09/2026 30/11/2026</t>
+          <t xml:space="preserve">20/07/2026 7/09/2026</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Graham Barber</t>
+          <t xml:space="preserve">Graham Barber and; Rima Andrews</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
@@ -7401,12 +7401,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuesday</t>
+          <t xml:space="preserve">Monday</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2a Tue 2b Tue 2c Tue 2d Tue</t>
+          <t xml:space="preserve">1a Mon 1b Mon</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -7416,47 +7416,47 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">10:00</t>
+          <t xml:space="preserve">12:00</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tutorial Support</t>
+          <t xml:space="preserve">Teaching</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BSBCRT404 Apply advanced critical thinking to work processes | ICTICT426 Identify and evaluate emerging technologies and practices | ICTSAS432 Identify and resolve client ICT problems</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BSBCRT404, ICTICT426, ICTSAS432</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tutorial Support | Shanna on Campus</t>
+          <t xml:space="preserve">Graham on Campus</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-18</t>
+          <t xml:space="preserve">9-18</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">14/09/2026 30/11/2026</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaun Stummer Online; Shanna Roper F2F</t>
+          <t xml:space="preserve">Graham Barber</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2F/VOFF</t>
+          <t xml:space="preserve">F2F</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>
@@ -7503,52 +7503,52 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
+          <t xml:space="preserve">9:00</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
           <t xml:space="preserve">10:00</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3:30</t>
-        </is>
-      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teaching</t>
+          <t xml:space="preserve">Tutorial Support</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICTPRG440 Apply introductory programming skills in different languages | ICTWEB431 Create and style simple markup language</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICTPRG440, ICTWEB431</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Different assessments | Shanna on Campus</t>
+          <t xml:space="preserve">Tutorial Support | Shanna on Campus</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-11</t>
+          <t xml:space="preserve">1-18</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t xml:space="preserve">21/07/2026 13/10/2026</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaun Stummer; Shanna Roper</t>
+          <t xml:space="preserve">Shaun Stummer Online; Shanna Roper F2F</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2F</t>
+          <t xml:space="preserve">F2F/VOFF</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
@@ -7610,37 +7610,37 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICTPRG441 Apply skills in object-oriented design | ICTPRG444 Analyse software requirements</t>
+          <t xml:space="preserve">ICTPRG440 Apply introductory programming skills in different languages | ICTWEB431 Create and style simple markup language</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICTPRG441, ICTPRG444</t>
+          <t xml:space="preserve">ICTPRG440, ICTWEB431</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Different assessments | Shanna on Campus</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">12-18</t>
+          <t xml:space="preserve">1-11</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t xml:space="preserve">20/10/2026 3/12/2026</t>
+          <t xml:space="preserve">21/07/2026 13/10/2026</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaun Stummer</t>
+          <t xml:space="preserve">Shaun Stummer; Shanna Roper</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">F2F</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
     </row>
@@ -7677,17 +7677,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wednesday</t>
+          <t xml:space="preserve">Tuesday</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">3a Wed 3b Wed</t>
+          <t xml:space="preserve">2a Tue 2b Tue 2c Tue 2d Tue</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9:00</t>
+          <t xml:space="preserve">10:00</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICTDBS416 Create basic relational databases | ICTPRG431 Apply query language in relational databases</t>
+          <t xml:space="preserve">ICTPRG441 Apply skills in object-oriented design | ICTPRG444 Analyse software requirements</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICTDBS416, ICTPRG431</t>
+          <t xml:space="preserve">ICTPRG441, ICTPRG444</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7717,17 +7717,17 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-8</t>
+          <t xml:space="preserve">12-18</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t xml:space="preserve">22/07/2026 09/09/2026</t>
+          <t xml:space="preserve">20/10/2026 3/12/2026</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaun Stummer and Anu Joshi</t>
+          <t xml:space="preserve">Shaun Stummer</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICTPRG436 Develop mobile applications | ICTPRG437 Build a user interface | ICTICT449 Use version control systems in development environment</t>
+          <t xml:space="preserve">ICTDBS416 Create basic relational databases | ICTPRG431 Apply query language in relational databases</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICTPRG436, ICTPRG437, ICTICT449</t>
+          <t xml:space="preserve">ICTDBS416, ICTPRG431</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">9-18</t>
+          <t xml:space="preserve">1-8</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t xml:space="preserve">16/09/2026 2/12/2026</t>
+          <t xml:space="preserve">22/07/2026 09/09/2026</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
     </row>
@@ -7861,70 +7861,162 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Wednesday</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3a Wed 3b Wed</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9:00</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3:30</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teaching</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICTPRG436 Develop mobile applications | ICTPRG437 Build a user interface | ICTICT449 Use version control systems in development environment</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICTPRG436, ICTPRG437, ICTICT449</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9-18</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16/09/2026 2/12/2026</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shaun Stummer and Anu Joshi</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICT40120 Cert IV  Programming OUR.docx</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cert IV Programming</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICT40120</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S2 2026</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t xml:space="preserve">Thursday</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t xml:space="preserve">4a Thu</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">9:00</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t xml:space="preserve">3:30</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">Teaching</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTPRG302 Apply introductory programming techniques | ICTPRG432 Develop data driven Apps | ICTPRG439 Use pre-existing components | ICTPRG430 Apply introductory object-oriented language skills | ICTPRG433 Test software developments</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t xml:space="preserve">ICTPRG302, ICTPRG432, ICTPRG439, ICTPRG430, ICTPRG433</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
+      <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">1-18</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t xml:space="preserve">23/07/2026 3/12/2026</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t xml:space="preserve">Shaun Stummer and  Anu Joshi</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
+      <c r="P87" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="R87" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
@@ -8194,7 +8286,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Graham Barber</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -8281,12 +8373,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">21/07/2026 01/12/2026</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Graham Barber</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -8746,7 +8838,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Jennie Agustin</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -9029,7 +9121,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Anu Joshi</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -9397,7 +9489,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Graham Barber; Graham Barber; Anu Joshi</t>
+          <t xml:space="preserve">Graham Barber</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -9464,12 +9556,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICTCLD301 Evaluate Characteristics of Cloud Computing solutions and services | ICTICT310 Identify and use industry specific technologies.</t>
+          <t xml:space="preserve">ICTCLD301 Evaluate Characteristics of Cloud Computing solutions and services</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICTCLD301, ICTICT310</t>
+          <t xml:space="preserve">ICTCLD301</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -9479,17 +9571,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-14 14-18</t>
+          <t xml:space="preserve">10-14</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">24/09/2026 29/10/2026 5/11/2026 03/12/202</t>
+          <t xml:space="preserve">24/09/2026 29/10/2026</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Graham Barber</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -9505,6 +9597,98 @@
       <c r="R8" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICT30120 Cert III General VOF OUR.docx</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cert III General (VOFF)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICT30120</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S2 2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thursday</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3A Thu 3B Thu 3C Thu</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9:00</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2:30</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teaching</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICTICT310 Identify and use industry specific technologies.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICTICT310</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-18</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/11/2026 03/12/202</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anu Joshi</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VOFF</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
     </row>
@@ -16538,116 +16722,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NEEDS-TEACHER</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ICT30120 Cert III  General F2F OUR.docx</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cert III General (F2F)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Cert III General (F2F)] Tuesday 9:00-2:30 'ICTCLD301 Evaluate Characteristics of Cloud Computing Solutions and services. | BSBXCS303 Securely manage personally identifiable information and workplace information. | ICTICT313 Identify IP, ethics, and privacy policies in ICT environments.' has NO teacher.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NEEDS-TEACHER</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ICT30120 Cert III  General F2F OUR.docx</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cert III General (F2F)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Cert III General (F2F)] Tuesday 2:30-3:30 'Tutorial Support' has NO teacher.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NEEDS-TEACHER</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ICT30120 Cert III  General F2F OUR.docx</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cert III General (F2F)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Cert III General (F2F)] Thursday 9:00-2:30 'ICTPRG302 Apply introductory programming techniques.' has NO teacher.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NEEDS-TEACHER</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ICT30120 Cert III General VOF OUR.docx</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cert III General (VOFF)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Cert III General (VOFF)] Tuesday 9:00-2:30 'BSBCRT301 Develop and extend critical and creative thinking skills. | BSBXTW301 Work in a team. | ICTSAS305 Provide ICT advice to clients.' has NO teacher.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NEEDS-TEACHER</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ICT30120 Cert III General VOF OUR.docx</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cert III General (VOFF)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Cert III General (VOFF)] Thursday 9:00-2:30 'ICTCLD301 Evaluate Characteristics of Cloud Computing solutions and services | ICTICT310 Identify and use industry specific technologies.' has NO teacher.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/output/normalised.xlsx
+++ b/output/normalised.xlsx
@@ -143,7 +143,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -245,7 +245,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -449,7 +449,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">carried-dates</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6768,12 +6768,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7278,12 +7278,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -7890,12 +7890,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">carried-dates</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8706,12 +8706,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -9223,12 +9223,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -9733,12 +9733,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -9944,12 +9944,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -10352,12 +10352,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -10454,12 +10454,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -10556,12 +10556,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -10658,12 +10658,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -10971,12 +10971,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">carried-dates</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -11277,12 +11277,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">S2 2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">inferred</t>
+          <t xml:space="preserve">carried-dates</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -13642,7 +13642,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -13744,7 +13744,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -14356,7 +14356,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -14458,7 +14458,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -14662,7 +14662,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -14866,7 +14866,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -14968,7 +14968,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -15070,7 +15070,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -15383,7 +15383,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -15689,7 +15689,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -15995,7 +15995,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -16097,7 +16097,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -16301,7 +16301,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -16403,7 +16403,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -16505,7 +16505,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -16709,7 +16709,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -16811,7 +16811,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -17015,7 +17015,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -17226,7 +17226,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -17634,7 +17634,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -17736,7 +17736,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -17838,7 +17838,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -17940,7 +17940,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -18042,7 +18042,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -18246,7 +18246,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -18348,7 +18348,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">row</t>
+          <t xml:space="preserve">dates</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -18544,6 +18544,28 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WARN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICT30120 Cert III General VOF OUR.docx</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cert III General (VOFF)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[Cert III General (VOFF)] row 8 has a malformed date '03/12/202' (incomplete year) which was ignored. Fix it in the source document. Dates: 5/11/2026 03/12/202</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>